--- a/ExcelProject/LoginAdmin.xlsx
+++ b/ExcelProject/LoginAdmin.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="76">
   <si>
     <t>Execute</t>
   </si>
@@ -40,25 +40,31 @@
     <t>Revise</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>TC6:01</t>
+  </si>
+  <si>
+    <t>MJU6504106500</t>
+  </si>
+  <si>
+    <t>#Jame1234</t>
+  </si>
+  <si>
+    <t>เข้าสู่ระบบเรียบร้อย</t>
+  </si>
+  <si>
+    <t>เข้าสู่ระบบสำเร็จ (Admin)</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
     <t>N</t>
-  </si>
-  <si>
-    <t>TC6:01</t>
-  </si>
-  <si>
-    <t>MJU6504106500</t>
-  </si>
-  <si>
-    <t>#Jame1234</t>
-  </si>
-  <si>
-    <t>เข้าสู่ระบบเรียบร้อย</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>TC6:02</t>
@@ -704,46 +710,50 @@
         <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="22.5">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="22.5">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>11</v>
@@ -755,43 +765,43 @@
         <v>12</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22.5">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="22.5">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
@@ -803,89 +813,89 @@
         <v>12</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22.5">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="22.5">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="22.5">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="22.5">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>11</v>
@@ -897,46 +907,46 @@
         <v>12</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="22.5">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="22.5">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>12</v>
@@ -945,22 +955,22 @@
         <v>12</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H12" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="22.5">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>12</v>
@@ -969,22 +979,22 @@
         <v>12</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="22.5">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>12</v>
@@ -993,22 +1003,22 @@
         <v>12</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="22.5">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>12</v>
@@ -1017,67 +1027,67 @@
         <v>12</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H15" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="22.5">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H16" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="22.5">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="22.5">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>11</v>
@@ -1089,43 +1099,43 @@
         <v>12</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="22.5">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H19" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="23.25">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>11</v>
@@ -1137,53 +1147,53 @@
         <v>12</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H20" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="22.5">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H21" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="23.25">
       <c r="A22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H22" s="4"/>
     </row>

--- a/ExcelProject/LoginAdmin.xlsx
+++ b/ExcelProject/LoginAdmin.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="75">
   <si>
     <t>Execute</t>
   </si>
@@ -40,87 +40,81 @@
     <t>Revise</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>TC6:01</t>
+  </si>
+  <si>
+    <t>MJU6504106500</t>
+  </si>
+  <si>
+    <t>#Jame1234</t>
+  </si>
+  <si>
+    <t>เข้าสู่ระบบสำเร็จ (Admin)</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>TC6:02</t>
+  </si>
+  <si>
+    <t>Jalem4544471</t>
+  </si>
+  <si>
+    <t>กรุณากรอกข้อมูลอีเมล์ให้อยู่ในรูปแบบของ MJU เช่น (MJU6504106001@mju.ac.th)</t>
+  </si>
+  <si>
+    <t>ความยาวอีเมล นักศึกษาต้องมี 13 ตัวพอดี</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>TC6:03</t>
+  </si>
+  <si>
+    <t>MJU6504106501</t>
+  </si>
+  <si>
+    <t>TC6:04</t>
+  </si>
+  <si>
+    <t>MJU 6504106336</t>
+  </si>
+  <si>
+    <t>กรุณากรอกข้อมูลโดยห้ามมีช่องว่าง</t>
+  </si>
+  <si>
+    <t>TC6:05</t>
+  </si>
+  <si>
+    <t>mju6504106502</t>
+  </si>
+  <si>
+    <t>TC6:06</t>
+  </si>
+  <si>
+    <t>mju650410633</t>
+  </si>
+  <si>
+    <t>TC6:07</t>
+  </si>
+  <si>
+    <t>mju65041063361</t>
+  </si>
+  <si>
+    <t>TC6:08</t>
+  </si>
+  <si>
+    <t>กรุณากรอกอีเมล</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>TC6:01</t>
-  </si>
-  <si>
-    <t>MJU6504106500</t>
-  </si>
-  <si>
-    <t>#Jame1234</t>
-  </si>
-  <si>
-    <t>เข้าสู่ระบบเรียบร้อย</t>
-  </si>
-  <si>
-    <t>เข้าสู่ระบบสำเร็จ (Admin)</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>TC6:02</t>
-  </si>
-  <si>
-    <t>Jalem4544471</t>
-  </si>
-  <si>
-    <t>กรุณากรอกข้อมูลอีเมล์ให้อยู่ในรูปแบบของ MJU เช่น (MJU6504106001@mju.ac.th)</t>
-  </si>
-  <si>
-    <t>ความยาวรหัสนักศึกษาต้องมี 13 ตัวพอดี</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>TC6:03</t>
-  </si>
-  <si>
-    <t>MJU6504106501</t>
-  </si>
-  <si>
-    <t>TC6:04</t>
-  </si>
-  <si>
-    <t>MJU 6504106336</t>
-  </si>
-  <si>
-    <t>กรุณากรอกข้อมูลโดยห้ามมีช่องว่าง</t>
-  </si>
-  <si>
-    <t>TC6:05</t>
-  </si>
-  <si>
-    <t>mju6504106502</t>
-  </si>
-  <si>
-    <t>TC6:06</t>
-  </si>
-  <si>
-    <t>mju650410633</t>
-  </si>
-  <si>
-    <t>TC6:07</t>
-  </si>
-  <si>
-    <t>mju65041063361</t>
-  </si>
-  <si>
-    <t>TC6:08</t>
-  </si>
-  <si>
-    <t>กรุณากรอกอีเมล</t>
-  </si>
-  <si>
     <t>TC6:09</t>
   </si>
   <si>
@@ -187,7 +181,7 @@
     <t>#Jame12</t>
   </si>
   <si>
-    <t>รหัสผ่านต้องมีความยาวระหว่าง 8 - 16 ตัวอักษร</t>
+    <t>รหัสผ่านต้อง 8-16 ตัวอักษร</t>
   </si>
   <si>
     <t>TC6:16</t>
@@ -215,6 +209,9 @@
   </si>
   <si>
     <t>กรุณากรอกข้อมูลอีเมล์และรหัสผ่านโดยห้ามมีช่องว่าง</t>
+  </si>
+  <si>
+    <t>ห้ามมีช่องว่าง</t>
   </si>
   <si>
     <t>TC6:19</t>
@@ -662,12 +659,12 @@
     <col min="3" max="3" style="9" width="26.719285714285714" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="9" width="15.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="72.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="46.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="54.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="55.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="27.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="7.433571428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -710,98 +707,102 @@
         <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="22.5">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="22.5">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22.5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="22.5">
+        <v>18</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
@@ -813,89 +814,97 @@
         <v>12</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22.5">
+        <v>13</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="22.5">
+        <v>13</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="22.5">
+        <v>13</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
+      <c r="A10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="22.5">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>11</v>
@@ -907,187 +916,203 @@
         <v>12</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="22.5">
+        <v>13</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="G11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="C12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="22.5">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21.75">
+      <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="22.5">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="22.5">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
+      <c r="A15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="22.5">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="22.5">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="D16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="F16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
+      <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="22.5">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="D17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="E17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21.75">
+      <c r="A18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="C18" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="22.5">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>11</v>
@@ -1099,43 +1124,47 @@
         <v>12</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="22.5">
+        <v>13</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="21.75">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="E19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="G19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="22.5">
+      <c r="A20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="23.25">
-      <c r="A20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>11</v>
@@ -1147,55 +1176,61 @@
         <v>12</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="22.5">
+        <v>13</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21.75">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="22.5">
+      <c r="A22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="23.25">
-      <c r="A22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
